--- a/Telecom-Media.xlsx
+++ b/Telecom-Media.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{060A9940-7D17-4250-BBCF-A5EACA07D076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70532632-FE67-4264-8B95-4FB935139B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="56470" yWindow="4650" windowWidth="18350" windowHeight="15420" xr2:uid="{955744E3-B0A7-4B9E-8695-D2DFA826D962}"/>
+    <workbookView xWindow="2690" yWindow="2230" windowWidth="12730" windowHeight="17590" activeTab="1" xr2:uid="{955744E3-B0A7-4B9E-8695-D2DFA826D962}"/>
   </bookViews>
   <sheets>
     <sheet name="Telecom" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="123">
   <si>
     <t>Name</t>
   </si>
@@ -1658,9 +1658,6 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="B3" s="5" t="s">
         <v>6</v>
       </c>
@@ -1694,7 +1691,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4" t="s">
@@ -1710,9 +1707,6 @@
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
@@ -1726,9 +1720,6 @@
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="B6" t="s">
         <v>56</v>
       </c>
@@ -1742,9 +1733,6 @@
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="B7" s="5" t="s">
         <v>60</v>
       </c>
@@ -1778,7 +1766,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
@@ -1794,9 +1782,6 @@
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="B9" t="s">
         <v>40</v>
       </c>
@@ -1810,7 +1795,7 @@
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
@@ -1826,9 +1811,6 @@
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="B11" t="s">
         <v>79</v>
       </c>
@@ -1842,9 +1824,6 @@
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="B12" t="s">
         <v>106</v>
       </c>
@@ -1858,9 +1837,6 @@
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
       <c r="B13" t="s">
         <v>81</v>
       </c>
@@ -1874,9 +1850,6 @@
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="B14" t="s">
         <v>83</v>
       </c>
@@ -1890,9 +1863,6 @@
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>10</v>
-      </c>
       <c r="B15" t="s">
         <v>85</v>
       </c>
@@ -1906,9 +1876,6 @@
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="B16" t="s">
         <v>108</v>
       </c>
@@ -1916,10 +1883,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>10</v>
-      </c>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>113</v>
       </c>
@@ -1927,10 +1891,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>10</v>
-      </c>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>114</v>
       </c>
@@ -1938,10 +1899,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>10</v>
-      </c>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>118</v>
       </c>
